--- a/out/Attention_Base_repeat_3_000005.xlsx
+++ b/out/Attention_Base_repeat_3_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>6.558570929792915</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>6.558570929792915</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>7.158570929792915</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>7.158570929792915</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>7.158570929792915</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>0.01422621125862855</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>0.01422621125862855</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention_Base_repeat_3_000005.xlsx
+++ b/out/Attention_Base_repeat_3_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention_Base_repeat_3_000005.xlsx
+++ b/out/Attention_Base_repeat_3_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02004618383944035</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.02454348281025887</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.02215893380343914</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.02243591845035553</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01914963871240616</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01740140467882156</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01754031330347061</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01606586948037148</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01359580829739571</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0120320487767458</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01042756251990795</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.009124374017119408</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.007479852065443993</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006597422063350677</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.005758829414844513</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006872541271150112</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.007657138630747795</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01280811615288258</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01387392729520798</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01905685104429722</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.02192290499806404</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.02110471576452255</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01940213516354561</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01957020536065102</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01815767027437687</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01767046377062798</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01770877093076706</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01660332456231117</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01615637913346291</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01586241647601128</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.02109223231673241</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.02096282877027988</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02148196659982204</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.02073925174772739</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01973999664187431</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02011629566550255</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01911485567688942</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01859323307871819</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01836230978369713</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0180574394762516</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01783894561231136</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0170363187789917</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01627396233379841</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01607444882392883</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01537830382585526</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01496118865907192</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01471483614295721</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.014090396463871</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0137996356934309</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01321200281381607</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01314962469041348</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01277192123234272</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01241923030465841</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01246790960431099</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01205530110746622</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01281197555363178</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01256956346333027</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01260451786220074</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01258217077702284</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01224597543478012</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01227138936519623</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01151423715054989</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01115566305816174</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01065519265830517</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01010139845311642</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.009977119974792004</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.009586779400706291</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009189028292894363</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.009012851864099503</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.008706988766789436</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.007883861660957336</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.007586637511849403</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01024029031395912</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01025738194584846</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01342309452593327</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01390431821346283</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01437866594642401</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01366274245083332</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01372233778238297</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01392915099859238</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01432333327829838</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01528207212686539</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0145568773150444</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01557677797973156</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01550968736410141</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01511911768466234</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01822451688349247</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01795838214457035</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01782655343413353</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0170581266283989</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01730609685182571</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01706874370574951</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01692332327365875</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01755660772323608</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01824679784476757</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01816491037607193</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01811297610402107</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01814176887273788</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01777844130992889</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01812569610774517</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01874462887644768</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01876874640583992</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01880574785172939</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01946008205413818</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01981008239090443</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01899691671133041</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.01960515975952148</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.01880640909075737</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.01870347186923027</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.01779920607805252</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0174965113401413</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.01711699739098549</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02074413746595383</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01780097931623459</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.02268422394990921</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.02163361199200153</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0242873914539814</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.02230292931199074</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.01992575079202652</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01981158927083015</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0261355098336935</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.02670290693640709</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0370548740029335</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.02261314168572426</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.02089601755142212</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
